--- a/tools/importer/reports/import-menu-page.report.xlsx
+++ b/tools/importer/reports/import-menu-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>menu-eng.report.json</t>
   </si>
   <si>
-    <t>["columns-intro","columns-news","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","columns-service","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","cards-doormat","columns-links","columns-links"]</t>
+    <t>["columns-intro","columns-news","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","columns-service","columns-links","columns-links"]</t>
   </si>
   <si>
     <t>menu-eng</t>
@@ -52,7 +52,7 @@
     <t>menu-page</t>
   </si>
   <si>
-    <t>2026-04-22T18:35:20.489Z</t>
+    <t>2026-04-22T18:48:37.390Z</t>
   </si>
   <si>
     <t>Canada Border Services Agency</t>

--- a/tools/importer/reports/import-menu-page.report.xlsx
+++ b/tools/importer/reports/import-menu-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>menu-eng.report.json</t>
   </si>
   <si>
-    <t>["columns-intro","columns-news","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","columns-service","columns-links","columns-links"]</t>
+    <t>["columns-intro","columns-news","cards-leadership","cards-feature","cards-feature","columns-service","columns-links","columns-links","columns-links","columns-links","columns-links"]</t>
   </si>
   <si>
     <t>menu-eng</t>
@@ -52,7 +52,7 @@
     <t>menu-page</t>
   </si>
   <si>
-    <t>2026-04-22T18:48:37.390Z</t>
+    <t>2026-04-22T19:05:41.695Z</t>
   </si>
   <si>
     <t>Canada Border Services Agency</t>

--- a/tools/importer/reports/import-menu-page.report.xlsx
+++ b/tools/importer/reports/import-menu-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>menu-eng.report.json</t>
   </si>
   <si>
-    <t>["columns-intro","columns-news","cards-leadership","cards-feature","cards-feature","columns-service","columns-links","columns-links","columns-links","columns-links","columns-links"]</t>
+    <t>["columns-intro","columns-news","cards-leadership","cards-feature","columns-service","columns-links","columns-links","columns-links","columns-links","columns-links"]</t>
   </si>
   <si>
     <t>menu-eng</t>
@@ -52,7 +52,7 @@
     <t>menu-page</t>
   </si>
   <si>
-    <t>2026-04-22T19:05:41.695Z</t>
+    <t>2026-04-22T19:10:28.929Z</t>
   </si>
   <si>
     <t>Canada Border Services Agency</t>
